--- a/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfc6514337675497c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4f839128971d4e1c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4f839128971d4e1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3f50bd308f704e25"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3f50bd308f704e25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9569f447dd304e5a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9569f447dd304e5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reb1a46af776c416d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reb1a46af776c416d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R59006829e4124aed"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R59006829e4124aed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R11a0d52f033b4fbb"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R11a0d52f033b4fbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R89be8da639534b2a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R89be8da639534b2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R57dfece2d00a420c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R57dfece2d00a420c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R84d3f9ff050648bc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R84d3f9ff050648bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re7115fd800fb4ace"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re7115fd800fb4ace"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4f9078f6eb744810"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4f9078f6eb744810"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9315c8c23e5b4dee"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9315c8c23e5b4dee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb245646b5a414f63"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb245646b5a414f63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re132a6d3fe5c4e7f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re132a6d3fe5c4e7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R36aa686c30904321"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R36aa686c30904321"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R633d479fd1534404"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R633d479fd1534404"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7b169b24ba3d4021"/>
   </x:sheets>
 </x:workbook>
 </file>
